--- a/artfynd/A 24073-2025 artfynd.xlsx
+++ b/artfynd/A 24073-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,7 +780,7 @@
         <v>126025042</v>
       </c>
       <c r="B3" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1286,49 +1286,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126025900</v>
+        <v>126026207</v>
       </c>
       <c r="B8" t="n">
-        <v>98332</v>
+        <v>80071</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548748</v>
+        <v>548716</v>
       </c>
       <c r="R8" t="n">
-        <v>6944191</v>
+        <v>6944192</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,45 +1383,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126026207</v>
+        <v>126025900</v>
       </c>
       <c r="B9" t="n">
-        <v>80071</v>
+        <v>98334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548716</v>
+        <v>548748</v>
       </c>
       <c r="R9" t="n">
-        <v>6944192</v>
+        <v>6944191</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1691,7 +1691,7 @@
         <v>126024513</v>
       </c>
       <c r="B12" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>126024430</v>
       </c>
       <c r="B17" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126025931</v>
+        <v>126026911</v>
       </c>
       <c r="B24" t="n">
-        <v>78968</v>
+        <v>80071</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2910,38 +2910,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548748</v>
+        <v>548787</v>
       </c>
       <c r="R24" t="n">
-        <v>6944191</v>
+        <v>6944106</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2974,11 +2970,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Riklig förekomst i detta område</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3005,10 +2996,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126026911</v>
+        <v>126024351</v>
       </c>
       <c r="B25" t="n">
-        <v>80071</v>
+        <v>78968</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3016,34 +3007,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Getterån, Mpd</t>
+          <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548787</v>
+        <v>548953</v>
       </c>
       <c r="R25" t="n">
-        <v>6944106</v>
+        <v>6944045</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3076,6 +3067,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3102,7 +3098,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126024351</v>
+        <v>126025931</v>
       </c>
       <c r="B26" t="n">
         <v>78968</v>
@@ -3130,17 +3126,21 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bodvikberget, Mpd</t>
+          <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548953</v>
+        <v>548748</v>
       </c>
       <c r="R26" t="n">
-        <v>6944045</v>
+        <v>6944191</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav</t>
+          <t>Riklig förekomst i detta område</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3201,6 +3201,394 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126024884</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78727</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Getterån, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>548846</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6944059</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126026245</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78727</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Getterån, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>548716</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6944192</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126024238</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78727</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Bodvikberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>549017</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6944002</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126024551</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78727</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Bodvikberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>548933</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6944073</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24073-2025 artfynd.xlsx
+++ b/artfynd/A 24073-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126026171</v>
       </c>
       <c r="B2" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126025042</v>
       </c>
       <c r="B3" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>126024988</v>
       </c>
       <c r="B5" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>126025937</v>
       </c>
       <c r="B6" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>126026207</v>
       </c>
       <c r="B8" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>126025900</v>
       </c>
       <c r="B9" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>126024874</v>
       </c>
       <c r="B10" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>126024513</v>
       </c>
       <c r="B12" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>126024731</v>
       </c>
       <c r="B13" t="n">
-        <v>80099</v>
+        <v>80103</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>126024494</v>
       </c>
       <c r="B14" t="n">
-        <v>80099</v>
+        <v>80103</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>126026478</v>
       </c>
       <c r="B15" t="n">
-        <v>78969</v>
+        <v>78973</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>126025344</v>
       </c>
       <c r="B16" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>126024430</v>
       </c>
       <c r="B17" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>126023959</v>
       </c>
       <c r="B18" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>126025366</v>
       </c>
       <c r="B20" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>126024799</v>
       </c>
       <c r="B21" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>126026911</v>
       </c>
       <c r="B24" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>126024351</v>
       </c>
       <c r="B25" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>126025931</v>
       </c>
       <c r="B26" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>126024884</v>
       </c>
       <c r="B27" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>126026245</v>
       </c>
       <c r="B28" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>126024238</v>
       </c>
       <c r="B29" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>126024551</v>
       </c>
       <c r="B30" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 24073-2025 artfynd.xlsx
+++ b/artfynd/A 24073-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>126025042</v>
       </c>
       <c r="B3" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126024354</v>
+        <v>126024988</v>
       </c>
       <c r="B4" t="n">
-        <v>57651</v>
+        <v>80075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,39 +889,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bodvikberget, Mpd</t>
+          <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548953</v>
+        <v>548808</v>
       </c>
       <c r="R4" t="n">
-        <v>6944045</v>
+        <v>6944125</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,11 +949,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,10 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126024988</v>
+        <v>126024354</v>
       </c>
       <c r="B5" t="n">
-        <v>80075</v>
+        <v>57651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,34 +986,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Getterån, Mpd</t>
+          <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548808</v>
+        <v>548953</v>
       </c>
       <c r="R5" t="n">
-        <v>6944125</v>
+        <v>6944045</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,6 +1051,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1286,45 +1286,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126026207</v>
+        <v>126025900</v>
       </c>
       <c r="B8" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548716</v>
+        <v>548748</v>
       </c>
       <c r="R8" t="n">
-        <v>6944192</v>
+        <v>6944191</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,49 +1387,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126025900</v>
+        <v>126026207</v>
       </c>
       <c r="B9" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548748</v>
+        <v>548716</v>
       </c>
       <c r="R9" t="n">
-        <v>6944191</v>
+        <v>6944192</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1691,7 +1691,7 @@
         <v>126024513</v>
       </c>
       <c r="B12" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>126024430</v>
       </c>
       <c r="B17" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126026911</v>
+        <v>126024351</v>
       </c>
       <c r="B24" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2910,34 +2910,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Getterån, Mpd</t>
+          <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548787</v>
+        <v>548953</v>
       </c>
       <c r="R24" t="n">
-        <v>6944106</v>
+        <v>6944045</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2970,6 +2970,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2996,7 +3001,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126024351</v>
+        <v>126025931</v>
       </c>
       <c r="B25" t="n">
         <v>78972</v>
@@ -3024,17 +3029,21 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bodvikberget, Mpd</t>
+          <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548953</v>
+        <v>548748</v>
       </c>
       <c r="R25" t="n">
-        <v>6944045</v>
+        <v>6944191</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3071,7 +3080,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav</t>
+          <t>Riklig förekomst i detta område</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3098,10 +3107,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126025931</v>
+        <v>126026911</v>
       </c>
       <c r="B26" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3109,38 +3118,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548748</v>
+        <v>548787</v>
       </c>
       <c r="R26" t="n">
-        <v>6944191</v>
+        <v>6944106</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3173,11 +3178,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Riklig förekomst i detta område</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 24073-2025 artfynd.xlsx
+++ b/artfynd/A 24073-2025 artfynd.xlsx
@@ -878,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126024988</v>
+        <v>126024354</v>
       </c>
       <c r="B4" t="n">
-        <v>80075</v>
+        <v>57651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,34 +889,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Getterån, Mpd</t>
+          <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548808</v>
+        <v>548953</v>
       </c>
       <c r="R4" t="n">
-        <v>6944125</v>
+        <v>6944045</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,6 +954,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -975,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126024354</v>
+        <v>126024988</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>80075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,39 +996,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bodvikberget, Mpd</t>
+          <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548953</v>
+        <v>548808</v>
       </c>
       <c r="R5" t="n">
-        <v>6944045</v>
+        <v>6944125</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,11 +1056,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1286,49 +1286,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126025900</v>
+        <v>126026207</v>
       </c>
       <c r="B8" t="n">
-        <v>98339</v>
+        <v>80075</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548748</v>
+        <v>548716</v>
       </c>
       <c r="R8" t="n">
-        <v>6944191</v>
+        <v>6944192</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,45 +1383,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126026207</v>
+        <v>126025900</v>
       </c>
       <c r="B9" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548716</v>
+        <v>548748</v>
       </c>
       <c r="R9" t="n">
-        <v>6944192</v>
+        <v>6944191</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,50 +1581,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126024923</v>
+        <v>126024513</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>98339</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Getterån, Mpd</t>
+          <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548808</v>
+        <v>548931</v>
       </c>
       <c r="R11" t="n">
-        <v>6944125</v>
+        <v>6944062</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1657,11 +1656,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1688,49 +1682,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126024513</v>
+        <v>126024923</v>
       </c>
       <c r="B12" t="n">
-        <v>98339</v>
+        <v>57651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bodvikberget, Mpd</t>
+          <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548931</v>
+        <v>548808</v>
       </c>
       <c r="R12" t="n">
-        <v>6944062</v>
+        <v>6944125</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1763,6 +1758,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2899,10 +2899,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126024351</v>
+        <v>126026911</v>
       </c>
       <c r="B24" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2910,34 +2910,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bodvikberget, Mpd</t>
+          <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548953</v>
+        <v>548787</v>
       </c>
       <c r="R24" t="n">
-        <v>6944045</v>
+        <v>6944106</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2970,11 +2970,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3001,7 +2996,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126025931</v>
+        <v>126024351</v>
       </c>
       <c r="B25" t="n">
         <v>78972</v>
@@ -3029,21 +3024,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Getterån, Mpd</t>
+          <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548748</v>
+        <v>548953</v>
       </c>
       <c r="R25" t="n">
-        <v>6944191</v>
+        <v>6944045</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3080,7 +3071,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Riklig förekomst i detta område</t>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3107,10 +3098,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126026911</v>
+        <v>126025931</v>
       </c>
       <c r="B26" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3118,34 +3109,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548787</v>
+        <v>548748</v>
       </c>
       <c r="R26" t="n">
-        <v>6944106</v>
+        <v>6944191</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3178,6 +3173,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Riklig förekomst i detta område</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 24073-2025 artfynd.xlsx
+++ b/artfynd/A 24073-2025 artfynd.xlsx
@@ -878,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126024354</v>
+        <v>126024988</v>
       </c>
       <c r="B4" t="n">
-        <v>57651</v>
+        <v>80075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,39 +889,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bodvikberget, Mpd</t>
+          <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548953</v>
+        <v>548808</v>
       </c>
       <c r="R4" t="n">
-        <v>6944045</v>
+        <v>6944125</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,11 +949,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,10 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126024988</v>
+        <v>126024354</v>
       </c>
       <c r="B5" t="n">
-        <v>80075</v>
+        <v>57651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,34 +986,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Getterån, Mpd</t>
+          <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548808</v>
+        <v>548953</v>
       </c>
       <c r="R5" t="n">
-        <v>6944125</v>
+        <v>6944045</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,6 +1051,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 24073-2025 artfynd.xlsx
+++ b/artfynd/A 24073-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126026171</v>
       </c>
       <c r="B2" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126025042</v>
       </c>
       <c r="B3" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126024988</v>
+        <v>126024354</v>
       </c>
       <c r="B4" t="n">
-        <v>80075</v>
+        <v>57652</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,34 +889,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Getterån, Mpd</t>
+          <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548808</v>
+        <v>548953</v>
       </c>
       <c r="R4" t="n">
-        <v>6944125</v>
+        <v>6944045</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,6 +954,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -975,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126024354</v>
+        <v>126024988</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>80076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,39 +996,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bodvikberget, Mpd</t>
+          <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548953</v>
+        <v>548808</v>
       </c>
       <c r="R5" t="n">
-        <v>6944045</v>
+        <v>6944125</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,11 +1056,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1085,7 +1085,7 @@
         <v>126025937</v>
       </c>
       <c r="B6" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>126024774</v>
       </c>
       <c r="B7" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>126026207</v>
       </c>
       <c r="B8" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>126025900</v>
       </c>
       <c r="B9" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>126024874</v>
       </c>
       <c r="B10" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>126024513</v>
       </c>
       <c r="B11" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>126024923</v>
       </c>
       <c r="B12" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>126024731</v>
       </c>
       <c r="B13" t="n">
-        <v>80103</v>
+        <v>80104</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>126024494</v>
       </c>
       <c r="B14" t="n">
-        <v>80103</v>
+        <v>80104</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>126026478</v>
       </c>
       <c r="B15" t="n">
-        <v>78973</v>
+        <v>78974</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>126025344</v>
       </c>
       <c r="B16" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>126024430</v>
       </c>
       <c r="B17" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>126023959</v>
       </c>
       <c r="B18" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>126026871</v>
       </c>
       <c r="B19" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>126025366</v>
       </c>
       <c r="B20" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>126024799</v>
       </c>
       <c r="B21" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>126025711</v>
       </c>
       <c r="B22" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>126026727</v>
       </c>
       <c r="B23" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>126026911</v>
       </c>
       <c r="B24" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>126024351</v>
       </c>
       <c r="B25" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>126025931</v>
       </c>
       <c r="B26" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>126024884</v>
       </c>
       <c r="B27" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>126026245</v>
       </c>
       <c r="B28" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>126024238</v>
       </c>
       <c r="B29" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>126024551</v>
       </c>
       <c r="B30" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 24073-2025 artfynd.xlsx
+++ b/artfynd/A 24073-2025 artfynd.xlsx
@@ -1581,49 +1581,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126024513</v>
+        <v>126024923</v>
       </c>
       <c r="B11" t="n">
-        <v>98341</v>
+        <v>57652</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bodvikberget, Mpd</t>
+          <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548931</v>
+        <v>548808</v>
       </c>
       <c r="R11" t="n">
-        <v>6944062</v>
+        <v>6944125</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1656,6 +1657,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1682,50 +1688,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126024923</v>
+        <v>126024513</v>
       </c>
       <c r="B12" t="n">
-        <v>57652</v>
+        <v>98341</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Getterån, Mpd</t>
+          <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548808</v>
+        <v>548931</v>
       </c>
       <c r="R12" t="n">
-        <v>6944125</v>
+        <v>6944062</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1758,11 +1763,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 24073-2025 artfynd.xlsx
+++ b/artfynd/A 24073-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>126025042</v>
       </c>
       <c r="B3" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126024354</v>
+        <v>126024988</v>
       </c>
       <c r="B4" t="n">
-        <v>57652</v>
+        <v>80076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,39 +889,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bodvikberget, Mpd</t>
+          <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548953</v>
+        <v>548808</v>
       </c>
       <c r="R4" t="n">
-        <v>6944045</v>
+        <v>6944125</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,11 +949,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,10 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126024988</v>
+        <v>126024354</v>
       </c>
       <c r="B5" t="n">
-        <v>80076</v>
+        <v>57652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,34 +986,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Getterån, Mpd</t>
+          <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548808</v>
+        <v>548953</v>
       </c>
       <c r="R5" t="n">
-        <v>6944125</v>
+        <v>6944045</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,6 +1051,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1286,45 +1286,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126026207</v>
+        <v>126025900</v>
       </c>
       <c r="B8" t="n">
-        <v>80076</v>
+        <v>98343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548716</v>
+        <v>548748</v>
       </c>
       <c r="R8" t="n">
-        <v>6944192</v>
+        <v>6944191</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,49 +1387,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126025900</v>
+        <v>126026207</v>
       </c>
       <c r="B9" t="n">
-        <v>98341</v>
+        <v>80076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548748</v>
+        <v>548716</v>
       </c>
       <c r="R9" t="n">
-        <v>6944191</v>
+        <v>6944192</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1691,7 +1691,7 @@
         <v>126024513</v>
       </c>
       <c r="B12" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>126024430</v>
       </c>
       <c r="B17" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126026911</v>
+        <v>126024351</v>
       </c>
       <c r="B24" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2910,34 +2910,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Getterån, Mpd</t>
+          <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548787</v>
+        <v>548953</v>
       </c>
       <c r="R24" t="n">
-        <v>6944106</v>
+        <v>6944045</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2970,6 +2970,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2996,10 +3001,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126024351</v>
+        <v>126026911</v>
       </c>
       <c r="B25" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3007,34 +3012,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bodvikberget, Mpd</t>
+          <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548953</v>
+        <v>548787</v>
       </c>
       <c r="R25" t="n">
-        <v>6944045</v>
+        <v>6944106</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3067,11 +3072,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 24073-2025 artfynd.xlsx
+++ b/artfynd/A 24073-2025 artfynd.xlsx
@@ -1286,49 +1286,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126025900</v>
+        <v>126026207</v>
       </c>
       <c r="B8" t="n">
-        <v>98343</v>
+        <v>80076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548748</v>
+        <v>548716</v>
       </c>
       <c r="R8" t="n">
-        <v>6944191</v>
+        <v>6944192</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,45 +1383,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126026207</v>
+        <v>126025900</v>
       </c>
       <c r="B9" t="n">
-        <v>80076</v>
+        <v>98343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548716</v>
+        <v>548748</v>
       </c>
       <c r="R9" t="n">
-        <v>6944192</v>
+        <v>6944191</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 24073-2025 artfynd.xlsx
+++ b/artfynd/A 24073-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126026171</v>
+        <v>126025042</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>98345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548716</v>
+        <v>548842</v>
       </c>
       <c r="R2" t="n">
-        <v>6944192</v>
+        <v>6944075</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +750,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,49 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126025042</v>
+        <v>126026171</v>
       </c>
       <c r="B3" t="n">
-        <v>98343</v>
+        <v>78973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548842</v>
+        <v>548716</v>
       </c>
       <c r="R3" t="n">
-        <v>6944075</v>
+        <v>6944192</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,6 +847,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1386,7 +1386,7 @@
         <v>126025900</v>
       </c>
       <c r="B9" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>126024513</v>
       </c>
       <c r="B12" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>126024430</v>
       </c>
       <c r="B17" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3001,10 +3001,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126026911</v>
+        <v>126025931</v>
       </c>
       <c r="B25" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3012,34 +3012,38 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548787</v>
+        <v>548748</v>
       </c>
       <c r="R25" t="n">
-        <v>6944106</v>
+        <v>6944191</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3072,6 +3076,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Riklig förekomst i detta område</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3098,10 +3107,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126025931</v>
+        <v>126026911</v>
       </c>
       <c r="B26" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3109,38 +3118,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548748</v>
+        <v>548787</v>
       </c>
       <c r="R26" t="n">
-        <v>6944191</v>
+        <v>6944106</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3173,11 +3178,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Riklig förekomst i detta område</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 24073-2025 artfynd.xlsx
+++ b/artfynd/A 24073-2025 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126025042</v>
+        <v>126026171</v>
       </c>
       <c r="B2" t="n">
-        <v>98345</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548842</v>
+        <v>548716</v>
       </c>
       <c r="R2" t="n">
-        <v>6944075</v>
+        <v>6944192</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,45 +777,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126026171</v>
+        <v>126025042</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>98349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548716</v>
+        <v>548842</v>
       </c>
       <c r="R3" t="n">
-        <v>6944192</v>
+        <v>6944075</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,11 +852,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,7 +881,7 @@
         <v>126024988</v>
       </c>
       <c r="B4" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>126024354</v>
       </c>
       <c r="B5" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>126025937</v>
       </c>
       <c r="B6" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>126024774</v>
       </c>
       <c r="B7" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>126026207</v>
       </c>
       <c r="B8" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>126025900</v>
       </c>
       <c r="B9" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>126024874</v>
       </c>
       <c r="B10" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>126024923</v>
       </c>
       <c r="B11" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>126024513</v>
       </c>
       <c r="B12" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126024731</v>
+        <v>126024494</v>
       </c>
       <c r="B13" t="n">
-        <v>80104</v>
+        <v>80108</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1820,14 +1820,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Getterån, Mpd</t>
+          <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>548888</v>
+        <v>548933</v>
       </c>
       <c r="R13" t="n">
-        <v>6944070</v>
+        <v>6944073</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1886,10 +1886,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126024494</v>
+        <v>126024731</v>
       </c>
       <c r="B14" t="n">
-        <v>80104</v>
+        <v>80108</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1917,14 +1917,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bodvikberget, Mpd</t>
+          <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548933</v>
+        <v>548888</v>
       </c>
       <c r="R14" t="n">
-        <v>6944073</v>
+        <v>6944070</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,7 +1986,7 @@
         <v>126026478</v>
       </c>
       <c r="B15" t="n">
-        <v>78974</v>
+        <v>78978</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>126025344</v>
       </c>
       <c r="B16" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>126024430</v>
       </c>
       <c r="B17" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>126023959</v>
       </c>
       <c r="B18" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>126026871</v>
       </c>
       <c r="B19" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>126025366</v>
       </c>
       <c r="B20" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>126024799</v>
       </c>
       <c r="B21" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>126025711</v>
       </c>
       <c r="B22" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>126026727</v>
       </c>
       <c r="B23" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126024351</v>
+        <v>126026911</v>
       </c>
       <c r="B24" t="n">
-        <v>78973</v>
+        <v>80080</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2910,34 +2910,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bodvikberget, Mpd</t>
+          <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548953</v>
+        <v>548787</v>
       </c>
       <c r="R24" t="n">
-        <v>6944045</v>
+        <v>6944106</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2970,11 +2970,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3001,10 +2996,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126025931</v>
+        <v>126024351</v>
       </c>
       <c r="B25" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3029,21 +3024,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Getterån, Mpd</t>
+          <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548748</v>
+        <v>548953</v>
       </c>
       <c r="R25" t="n">
-        <v>6944191</v>
+        <v>6944045</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3080,7 +3071,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Riklig förekomst i detta område</t>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3107,10 +3098,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126026911</v>
+        <v>126025931</v>
       </c>
       <c r="B26" t="n">
-        <v>80076</v>
+        <v>78977</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3118,34 +3109,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548787</v>
+        <v>548748</v>
       </c>
       <c r="R26" t="n">
-        <v>6944106</v>
+        <v>6944191</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3178,6 +3173,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Riklig förekomst i detta område</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3207,7 +3207,7 @@
         <v>126024884</v>
       </c>
       <c r="B27" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>126026245</v>
       </c>
       <c r="B28" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>126024238</v>
       </c>
       <c r="B29" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>126024551</v>
       </c>
       <c r="B30" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 24073-2025 artfynd.xlsx
+++ b/artfynd/A 24073-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126026171</v>
+        <v>126025042</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>98349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548716</v>
+        <v>548842</v>
       </c>
       <c r="R2" t="n">
-        <v>6944192</v>
+        <v>6944075</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +750,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,49 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126025042</v>
+        <v>126026171</v>
       </c>
       <c r="B3" t="n">
-        <v>98349</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548842</v>
+        <v>548716</v>
       </c>
       <c r="R3" t="n">
-        <v>6944075</v>
+        <v>6944192</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,6 +847,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 24073-2025 artfynd.xlsx
+++ b/artfynd/A 24073-2025 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126025042</v>
+        <v>126026171</v>
       </c>
       <c r="B2" t="n">
-        <v>98349</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548842</v>
+        <v>548716</v>
       </c>
       <c r="R2" t="n">
-        <v>6944075</v>
+        <v>6944192</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,45 +777,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126026171</v>
+        <v>126025042</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548716</v>
+        <v>548842</v>
       </c>
       <c r="R3" t="n">
-        <v>6944192</v>
+        <v>6944075</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,11 +852,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1386,7 +1386,7 @@
         <v>126025900</v>
       </c>
       <c r="B9" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>126024513</v>
       </c>
       <c r="B12" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126024494</v>
+        <v>126024731</v>
       </c>
       <c r="B13" t="n">
         <v>80108</v>
@@ -1820,14 +1820,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bodvikberget, Mpd</t>
+          <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>548933</v>
+        <v>548888</v>
       </c>
       <c r="R13" t="n">
-        <v>6944073</v>
+        <v>6944070</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1886,7 +1886,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126024731</v>
+        <v>126024494</v>
       </c>
       <c r="B14" t="n">
         <v>80108</v>
@@ -1917,14 +1917,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Getterån, Mpd</t>
+          <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548888</v>
+        <v>548933</v>
       </c>
       <c r="R14" t="n">
-        <v>6944070</v>
+        <v>6944073</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2189,7 +2189,7 @@
         <v>126024430</v>
       </c>
       <c r="B17" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 24073-2025 artfynd.xlsx
+++ b/artfynd/A 24073-2025 artfynd.xlsx
@@ -1286,45 +1286,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126026207</v>
+        <v>126025900</v>
       </c>
       <c r="B8" t="n">
-        <v>80080</v>
+        <v>98352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548716</v>
+        <v>548748</v>
       </c>
       <c r="R8" t="n">
-        <v>6944192</v>
+        <v>6944191</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,49 +1387,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126025900</v>
+        <v>126026207</v>
       </c>
       <c r="B9" t="n">
-        <v>98352</v>
+        <v>80080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548748</v>
+        <v>548716</v>
       </c>
       <c r="R9" t="n">
-        <v>6944191</v>
+        <v>6944192</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 24073-2025 artfynd.xlsx
+++ b/artfynd/A 24073-2025 artfynd.xlsx
@@ -1286,49 +1286,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126025900</v>
+        <v>126026207</v>
       </c>
       <c r="B8" t="n">
-        <v>98352</v>
+        <v>80080</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548748</v>
+        <v>548716</v>
       </c>
       <c r="R8" t="n">
-        <v>6944191</v>
+        <v>6944192</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,45 +1383,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126026207</v>
+        <v>126025900</v>
       </c>
       <c r="B9" t="n">
-        <v>80080</v>
+        <v>98352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548716</v>
+        <v>548748</v>
       </c>
       <c r="R9" t="n">
-        <v>6944192</v>
+        <v>6944191</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,50 +1581,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126024923</v>
+        <v>126024513</v>
       </c>
       <c r="B11" t="n">
-        <v>57656</v>
+        <v>98352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Getterån, Mpd</t>
+          <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548808</v>
+        <v>548931</v>
       </c>
       <c r="R11" t="n">
-        <v>6944125</v>
+        <v>6944062</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1657,11 +1656,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1688,49 +1682,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126024513</v>
+        <v>126024923</v>
       </c>
       <c r="B12" t="n">
-        <v>98352</v>
+        <v>57656</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bodvikberget, Mpd</t>
+          <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548931</v>
+        <v>548808</v>
       </c>
       <c r="R12" t="n">
-        <v>6944062</v>
+        <v>6944125</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1763,6 +1758,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2899,10 +2899,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126026911</v>
+        <v>126024351</v>
       </c>
       <c r="B24" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2910,34 +2910,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Getterån, Mpd</t>
+          <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548787</v>
+        <v>548953</v>
       </c>
       <c r="R24" t="n">
-        <v>6944106</v>
+        <v>6944045</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2970,6 +2970,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2996,7 +3001,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126024351</v>
+        <v>126025931</v>
       </c>
       <c r="B25" t="n">
         <v>78977</v>
@@ -3024,17 +3029,21 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bodvikberget, Mpd</t>
+          <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548953</v>
+        <v>548748</v>
       </c>
       <c r="R25" t="n">
-        <v>6944045</v>
+        <v>6944191</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3071,7 +3080,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav</t>
+          <t>Riklig förekomst i detta område</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3098,10 +3107,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126025931</v>
+        <v>126026911</v>
       </c>
       <c r="B26" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3109,38 +3118,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548748</v>
+        <v>548787</v>
       </c>
       <c r="R26" t="n">
-        <v>6944191</v>
+        <v>6944106</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3173,11 +3178,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Riklig förekomst i detta område</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 24073-2025 artfynd.xlsx
+++ b/artfynd/A 24073-2025 artfynd.xlsx
@@ -1581,49 +1581,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126024513</v>
+        <v>126024923</v>
       </c>
       <c r="B11" t="n">
-        <v>98352</v>
+        <v>57656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bodvikberget, Mpd</t>
+          <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548931</v>
+        <v>548808</v>
       </c>
       <c r="R11" t="n">
-        <v>6944062</v>
+        <v>6944125</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1656,6 +1657,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1682,50 +1688,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126024923</v>
+        <v>126024513</v>
       </c>
       <c r="B12" t="n">
-        <v>57656</v>
+        <v>98352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Getterån, Mpd</t>
+          <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548808</v>
+        <v>548931</v>
       </c>
       <c r="R12" t="n">
-        <v>6944125</v>
+        <v>6944062</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1758,11 +1763,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 24073-2025 artfynd.xlsx
+++ b/artfynd/A 24073-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126026171</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126025042</v>
       </c>
       <c r="B3" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>126024988</v>
       </c>
       <c r="B4" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>126024354</v>
       </c>
       <c r="B5" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>126025937</v>
       </c>
       <c r="B6" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>126024774</v>
       </c>
       <c r="B7" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,45 +1286,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126026207</v>
+        <v>126025900</v>
       </c>
       <c r="B8" t="n">
-        <v>80080</v>
+        <v>98361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548716</v>
+        <v>548748</v>
       </c>
       <c r="R8" t="n">
-        <v>6944192</v>
+        <v>6944191</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,49 +1387,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126025900</v>
+        <v>126026207</v>
       </c>
       <c r="B9" t="n">
-        <v>98352</v>
+        <v>80083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548748</v>
+        <v>548716</v>
       </c>
       <c r="R9" t="n">
-        <v>6944191</v>
+        <v>6944192</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1487,7 +1487,7 @@
         <v>126024874</v>
       </c>
       <c r="B10" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>126024923</v>
       </c>
       <c r="B11" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>126024513</v>
       </c>
       <c r="B12" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>126024731</v>
       </c>
       <c r="B13" t="n">
-        <v>80108</v>
+        <v>80111</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>126024494</v>
       </c>
       <c r="B14" t="n">
-        <v>80108</v>
+        <v>80111</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>126026478</v>
       </c>
       <c r="B15" t="n">
-        <v>78978</v>
+        <v>78981</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>126025344</v>
       </c>
       <c r="B16" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>126024430</v>
       </c>
       <c r="B17" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>126023959</v>
       </c>
       <c r="B18" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>126026871</v>
       </c>
       <c r="B19" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>126025366</v>
       </c>
       <c r="B20" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>126024799</v>
       </c>
       <c r="B21" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>126025711</v>
       </c>
       <c r="B22" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>126026727</v>
       </c>
       <c r="B23" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126024351</v>
+        <v>126026911</v>
       </c>
       <c r="B24" t="n">
-        <v>78977</v>
+        <v>80083</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2910,34 +2910,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bodvikberget, Mpd</t>
+          <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548953</v>
+        <v>548787</v>
       </c>
       <c r="R24" t="n">
-        <v>6944045</v>
+        <v>6944106</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2970,11 +2970,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3001,10 +2996,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126025931</v>
+        <v>126024351</v>
       </c>
       <c r="B25" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3029,21 +3024,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Getterån, Mpd</t>
+          <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548748</v>
+        <v>548953</v>
       </c>
       <c r="R25" t="n">
-        <v>6944191</v>
+        <v>6944045</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3080,7 +3071,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Riklig förekomst i detta område</t>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3107,10 +3098,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126026911</v>
+        <v>126025931</v>
       </c>
       <c r="B26" t="n">
-        <v>80080</v>
+        <v>78980</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3118,34 +3109,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548787</v>
+        <v>548748</v>
       </c>
       <c r="R26" t="n">
-        <v>6944106</v>
+        <v>6944191</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3178,6 +3173,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Riklig förekomst i detta område</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3207,7 +3207,7 @@
         <v>126024884</v>
       </c>
       <c r="B27" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>126026245</v>
       </c>
       <c r="B28" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>126024238</v>
       </c>
       <c r="B29" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>126024551</v>
       </c>
       <c r="B30" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 24073-2025 artfynd.xlsx
+++ b/artfynd/A 24073-2025 artfynd.xlsx
@@ -878,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126024988</v>
+        <v>126024354</v>
       </c>
       <c r="B4" t="n">
-        <v>80083</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,34 +889,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Getterån, Mpd</t>
+          <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548808</v>
+        <v>548953</v>
       </c>
       <c r="R4" t="n">
-        <v>6944125</v>
+        <v>6944045</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,6 +954,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -975,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126024354</v>
+        <v>126024988</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>80083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,39 +996,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bodvikberget, Mpd</t>
+          <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548953</v>
+        <v>548808</v>
       </c>
       <c r="R5" t="n">
-        <v>6944045</v>
+        <v>6944125</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,11 +1056,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1286,49 +1286,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126025900</v>
+        <v>126026207</v>
       </c>
       <c r="B8" t="n">
-        <v>98361</v>
+        <v>80083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548748</v>
+        <v>548716</v>
       </c>
       <c r="R8" t="n">
-        <v>6944191</v>
+        <v>6944192</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,45 +1383,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126026207</v>
+        <v>126025900</v>
       </c>
       <c r="B9" t="n">
-        <v>80083</v>
+        <v>98361</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548716</v>
+        <v>548748</v>
       </c>
       <c r="R9" t="n">
-        <v>6944192</v>
+        <v>6944191</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,50 +1581,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126024923</v>
+        <v>126024513</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>98361</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Getterån, Mpd</t>
+          <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548808</v>
+        <v>548931</v>
       </c>
       <c r="R11" t="n">
-        <v>6944125</v>
+        <v>6944062</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1657,11 +1656,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1688,49 +1682,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126024513</v>
+        <v>126024923</v>
       </c>
       <c r="B12" t="n">
-        <v>98361</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bodvikberget, Mpd</t>
+          <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548931</v>
+        <v>548808</v>
       </c>
       <c r="R12" t="n">
-        <v>6944062</v>
+        <v>6944125</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1763,6 +1758,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 24073-2025 artfynd.xlsx
+++ b/artfynd/A 24073-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126026171</v>
+        <v>126025042</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>98361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548716</v>
+        <v>548842</v>
       </c>
       <c r="R2" t="n">
-        <v>6944192</v>
+        <v>6944075</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +750,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,49 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126025042</v>
+        <v>126026171</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>78980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548842</v>
+        <v>548716</v>
       </c>
       <c r="R3" t="n">
-        <v>6944075</v>
+        <v>6944192</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,6 +847,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 24073-2025 artfynd.xlsx
+++ b/artfynd/A 24073-2025 artfynd.xlsx
@@ -878,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126024354</v>
+        <v>126024988</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>80083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,39 +889,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bodvikberget, Mpd</t>
+          <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548953</v>
+        <v>548808</v>
       </c>
       <c r="R4" t="n">
-        <v>6944045</v>
+        <v>6944125</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,11 +949,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,10 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126024988</v>
+        <v>126024354</v>
       </c>
       <c r="B5" t="n">
-        <v>80083</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,34 +986,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Getterån, Mpd</t>
+          <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548808</v>
+        <v>548953</v>
       </c>
       <c r="R5" t="n">
-        <v>6944125</v>
+        <v>6944045</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,6 +1051,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 24073-2025 artfynd.xlsx
+++ b/artfynd/A 24073-2025 artfynd.xlsx
@@ -1581,49 +1581,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126024513</v>
+        <v>126024923</v>
       </c>
       <c r="B11" t="n">
-        <v>98361</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bodvikberget, Mpd</t>
+          <t>Getterån, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548931</v>
+        <v>548808</v>
       </c>
       <c r="R11" t="n">
-        <v>6944062</v>
+        <v>6944125</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1656,6 +1657,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1682,50 +1688,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126024923</v>
+        <v>126024513</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>98361</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Getterån, Mpd</t>
+          <t>Bodvikberget, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548808</v>
+        <v>548931</v>
       </c>
       <c r="R12" t="n">
-        <v>6944125</v>
+        <v>6944062</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1758,11 +1763,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
